--- a/cards.xlsx
+++ b/cards.xlsx
@@ -67251,7 +67251,7 @@
         <v>4786</v>
       </c>
       <c r="R48" s="5" t="s">
-        <v>2275</v>
+        <v>34</v>
       </c>
       <c r="S48" s="5" t="s">
         <v>4787</v>
@@ -67319,7 +67319,7 @@
         <v>4794</v>
       </c>
       <c r="R49" s="5" t="s">
-        <v>2275</v>
+        <v>34</v>
       </c>
       <c r="S49" s="5" t="s">
         <v>4795</v>
@@ -67387,7 +67387,7 @@
         <v>96</v>
       </c>
       <c r="R50" s="5" t="s">
-        <v>2275</v>
+        <v>34</v>
       </c>
       <c r="S50" s="5" t="s">
         <v>4801</v>
@@ -67455,7 +67455,7 @@
         <v>930</v>
       </c>
       <c r="R51" s="5" t="s">
-        <v>2275</v>
+        <v>34</v>
       </c>
       <c r="S51" s="5" t="s">
         <v>4808</v>
@@ -67523,7 +67523,7 @@
         <v>4814</v>
       </c>
       <c r="R52" s="5" t="s">
-        <v>2275</v>
+        <v>34</v>
       </c>
       <c r="S52" s="5" t="s">
         <v>4815</v>
@@ -67591,7 +67591,7 @@
         <v>4821</v>
       </c>
       <c r="R53" s="5" t="s">
-        <v>2275</v>
+        <v>34</v>
       </c>
       <c r="S53" s="5" t="s">
         <v>4822</v>
@@ -67659,7 +67659,7 @@
         <v>4829</v>
       </c>
       <c r="R54" s="5" t="s">
-        <v>2275</v>
+        <v>34</v>
       </c>
       <c r="S54" s="5" t="s">
         <v>4494</v>
@@ -67727,7 +67727,7 @@
         <v>96</v>
       </c>
       <c r="R55" s="5" t="s">
-        <v>2275</v>
+        <v>34</v>
       </c>
       <c r="S55" s="5" t="s">
         <v>4835</v>
@@ -71195,7 +71195,7 @@
         <v>5123</v>
       </c>
       <c r="R106" s="5" t="s">
-        <v>2275</v>
+        <v>34</v>
       </c>
       <c r="S106" s="5" t="s">
         <v>5124</v>
@@ -71263,7 +71263,7 @@
         <v>5130</v>
       </c>
       <c r="R107" s="5" t="s">
-        <v>2275</v>
+        <v>34</v>
       </c>
       <c r="S107" s="5" t="s">
         <v>191</v>
@@ -71331,7 +71331,7 @@
         <v>96</v>
       </c>
       <c r="R108" s="5" t="s">
-        <v>2275</v>
+        <v>34</v>
       </c>
       <c r="S108" s="5" t="s">
         <v>5136</v>
@@ -71399,7 +71399,7 @@
         <v>323</v>
       </c>
       <c r="R109" s="5" t="s">
-        <v>2275</v>
+        <v>34</v>
       </c>
       <c r="S109" s="5" t="s">
         <v>5143</v>
@@ -71467,7 +71467,7 @@
         <v>2584</v>
       </c>
       <c r="R110" s="5" t="s">
-        <v>2275</v>
+        <v>34</v>
       </c>
       <c r="S110" s="5" t="s">
         <v>5149</v>
@@ -71535,7 +71535,7 @@
         <v>472</v>
       </c>
       <c r="R111" s="5" t="s">
-        <v>2275</v>
+        <v>34</v>
       </c>
       <c r="S111" s="5" t="s">
         <v>5155</v>
@@ -71603,7 +71603,7 @@
         <v>5162</v>
       </c>
       <c r="R112" s="5" t="s">
-        <v>2275</v>
+        <v>34</v>
       </c>
       <c r="S112" s="5" t="s">
         <v>5163</v>
@@ -71671,7 +71671,7 @@
         <v>483</v>
       </c>
       <c r="R113" s="5" t="s">
-        <v>2275</v>
+        <v>34</v>
       </c>
       <c r="S113" s="5" t="s">
         <v>5169</v>

--- a/cards.xlsx
+++ b/cards.xlsx
@@ -38170,7 +38170,7 @@
         <v>2180</v>
       </c>
       <c r="M90" s="5" t="s">
-        <v>339</v>
+        <v>34</v>
       </c>
       <c r="N90" s="5" t="s">
         <v>339</v>
@@ -38510,7 +38510,7 @@
         <v>2210</v>
       </c>
       <c r="M95" s="5" t="s">
-        <v>339</v>
+        <v>34</v>
       </c>
       <c r="N95" s="5" t="s">
         <v>339</v>
@@ -38578,7 +38578,7 @@
         <v>2217</v>
       </c>
       <c r="M96" s="5" t="s">
-        <v>339</v>
+        <v>34</v>
       </c>
       <c r="N96" s="5" t="s">
         <v>1818</v>
@@ -54404,7 +54404,7 @@
         <v>3672</v>
       </c>
       <c r="M94" s="5" t="s">
-        <v>339</v>
+        <v>34</v>
       </c>
       <c r="N94" s="5" t="s">
         <v>339</v>
@@ -62384,7 +62384,7 @@
         <v>4374</v>
       </c>
       <c r="M94" s="5" t="s">
-        <v>339</v>
+        <v>34</v>
       </c>
       <c r="N94" s="5" t="s">
         <v>339</v>
@@ -62452,7 +62452,7 @@
         <v>775</v>
       </c>
       <c r="M95" s="5" t="s">
-        <v>339</v>
+        <v>34</v>
       </c>
       <c r="N95" s="5" t="s">
         <v>4379</v>
@@ -62520,7 +62520,7 @@
         <v>4383</v>
       </c>
       <c r="M96" s="5" t="s">
-        <v>339</v>
+        <v>34</v>
       </c>
       <c r="N96" s="5" t="s">
         <v>339</v>
@@ -66216,7 +66216,7 @@
         <v>4691</v>
       </c>
       <c r="M33" s="5" t="s">
-        <v>339</v>
+        <v>34</v>
       </c>
       <c r="N33" s="5" t="s">
         <v>339</v>
@@ -66556,7 +66556,7 @@
         <v>4720</v>
       </c>
       <c r="M38" s="5" t="s">
-        <v>339</v>
+        <v>34</v>
       </c>
       <c r="N38" s="5" t="s">
         <v>339</v>
@@ -70092,7 +70092,7 @@
         <v>5020</v>
       </c>
       <c r="M90" s="5" t="s">
-        <v>339</v>
+        <v>34</v>
       </c>
       <c r="N90" s="5" t="s">
         <v>339</v>
@@ -70364,7 +70364,7 @@
         <v>5049</v>
       </c>
       <c r="M94" s="5" t="s">
-        <v>339</v>
+        <v>34</v>
       </c>
       <c r="N94" s="5" t="s">
         <v>339</v>
@@ -70432,7 +70432,7 @@
         <v>5055</v>
       </c>
       <c r="M95" s="5" t="s">
-        <v>339</v>
+        <v>34</v>
       </c>
       <c r="N95" s="5" t="s">
         <v>339</v>
